--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,9 +48,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -63,13 +63,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -78,30 +71,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -109,6 +87,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,31 +115,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,7 +140,52 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,26 +199,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,7 +215,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,7 +251,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,7 +263,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,13 +293,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,31 +311,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,19 +353,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,67 +377,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,11 +409,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -429,6 +435,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -462,21 +483,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -492,17 +498,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="B9">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="B10">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="C10">
         <v>4</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,8 +48,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -69,11 +69,56 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -92,8 +137,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -109,45 +163,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,38 +184,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,6 +198,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,7 +215,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,7 +233,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,13 +287,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,19 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,49 +365,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,61 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,21 +425,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -456,11 +441,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -476,9 +474,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,8 +501,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -755,7 +755,7 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>ネレイドジェム</v>
+            <v>スライム</v>
           </cell>
         </row>
         <row r="3">
@@ -795,7 +795,7 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>ネームレス</v>
+            <v>ビショップ</v>
           </cell>
         </row>
         <row r="8">
@@ -803,7 +803,7 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>サーチャー</v>
+            <v>スペクター</v>
           </cell>
         </row>
         <row r="9">
@@ -811,7 +811,7 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>シールド</v>
+            <v>タートルシェル</v>
           </cell>
         </row>
         <row r="10">
@@ -827,7 +827,7 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>スコーピオン</v>
+            <v>スティングレイ</v>
           </cell>
         </row>
         <row r="12">
@@ -835,7 +835,7 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>スクイッド</v>
+            <v>フィッシャーマン</v>
           </cell>
         </row>
         <row r="13">
@@ -843,7 +843,7 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>クリーパー</v>
+            <v>ブラックナイト</v>
           </cell>
         </row>
         <row r="14">
@@ -851,7 +851,7 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>インプ</v>
+            <v>サイクロプス</v>
           </cell>
         </row>
         <row r="15">
@@ -859,7 +859,7 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>ゴーストアーマー</v>
+            <v>スケルトン</v>
           </cell>
         </row>
         <row r="16">
@@ -867,7 +867,7 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>ソード</v>
+            <v>リザード</v>
           </cell>
         </row>
         <row r="17">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D3" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C3,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D4" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C4,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E4">
         <v>40</v>
@@ -1574,11 +1574,11 @@
         <v>1021</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C9,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スライム</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1601,11 +1601,11 @@
         <v>1021</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E30">
         <v>15</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ビショップ</v>
       </c>
       <c r="E52">
         <v>5</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ビショップ</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E57">
         <v>5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ビショップ</v>
       </c>
       <c r="E62">
         <v>5</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>サイクロプス</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ビショップ</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E67">
         <v>5</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スペクター</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E71">
         <v>5</v>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E74">
         <v>15</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E76">
         <v>5</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>リザード</v>
       </c>
       <c r="E82">
         <v>5</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E88">
         <v>5</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ビショップ</v>
       </c>
       <c r="E94">
         <v>5</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E99">
         <v>10</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E100">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E101">
         <v>10</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E102">
         <v>10</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E104">
         <v>20</v>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E105">
         <v>20</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E106">
         <v>20</v>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E107">
         <v>20</v>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スライム</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>スティングレイ</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="D124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C124,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>リザード</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="D127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C127,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>サイクロプス</v>
       </c>
       <c r="E127">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -76,6 +76,90 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -84,8 +168,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -101,106 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,7 +215,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,37 +233,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,67 +251,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,7 +269,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,7 +281,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,7 +299,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,7 +317,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +371,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,36 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -463,11 +433,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -479,6 +479,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -497,15 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -763,7 +763,7 @@
             <v>2</v>
           </cell>
           <cell r="B3" t="str">
-            <v>カースド</v>
+            <v>バット</v>
           </cell>
         </row>
         <row r="4">
@@ -771,7 +771,7 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>ビー</v>
+            <v>ホーネット</v>
           </cell>
         </row>
         <row r="5">
@@ -779,7 +779,7 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>ウルフ</v>
+            <v>スパイダー</v>
           </cell>
         </row>
         <row r="6">
@@ -787,7 +787,7 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>クロウ</v>
+            <v>ビッグラット</v>
           </cell>
         </row>
         <row r="7">
@@ -795,7 +795,7 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>ビショップ</v>
+            <v>ウィスプ</v>
           </cell>
         </row>
         <row r="8">
@@ -803,7 +803,7 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>スペクター</v>
+            <v>スネーク</v>
           </cell>
         </row>
         <row r="9">
@@ -811,7 +811,7 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>タートルシェル</v>
+            <v>スコーピオン</v>
           </cell>
         </row>
         <row r="10">
@@ -819,7 +819,7 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>ドライアド</v>
+            <v>ゼリーフィッシュ</v>
           </cell>
         </row>
         <row r="11">
@@ -827,7 +827,7 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>スティングレイ</v>
+            <v>マッドプラント</v>
           </cell>
         </row>
         <row r="12">
@@ -835,7 +835,7 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>フィッシャーマン</v>
+            <v>ゴースト</v>
           </cell>
         </row>
         <row r="13">
@@ -843,7 +843,7 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>ブラックナイト</v>
+            <v>スケルトン</v>
           </cell>
         </row>
         <row r="14">
@@ -851,7 +851,7 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>サイクロプス</v>
+            <v>オーク</v>
           </cell>
         </row>
         <row r="15">
@@ -859,7 +859,7 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>スケルトン</v>
+            <v>インプ</v>
           </cell>
         </row>
         <row r="16">
@@ -867,214 +867,310 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>リザード</v>
+            <v>ゲイザー</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17">
-            <v>101</v>
+            <v>16</v>
           </cell>
           <cell r="B17" t="str">
-            <v>アモン</v>
+            <v>パペット</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
-            <v>102</v>
+            <v>17</v>
           </cell>
           <cell r="B18" t="str">
-            <v>ベリト</v>
+            <v>ゾンビ</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19">
-            <v>103</v>
+            <v>18</v>
           </cell>
           <cell r="B19" t="str">
-            <v>パイモン</v>
+            <v>コカトリス</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>104</v>
+            <v>19</v>
           </cell>
           <cell r="B20" t="str">
-            <v>アンドラス</v>
+            <v>サハギン</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>105</v>
+            <v>20</v>
           </cell>
           <cell r="B21" t="str">
-            <v>ビフロンス</v>
+            <v>ウェアウルフ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>106</v>
+            <v>101</v>
           </cell>
           <cell r="B22" t="str">
-            <v>アイホート</v>
+            <v>ベヒーモス</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>107</v>
+            <v>102</v>
           </cell>
           <cell r="B23" t="str">
-            <v>ビヤーキー</v>
+            <v>ミノタウロス</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>201</v>
+            <v>103</v>
           </cell>
           <cell r="B24" t="str">
-            <v>アンリマユ</v>
+            <v>シルフ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>202</v>
+            <v>104</v>
           </cell>
           <cell r="B25" t="str">
-            <v>ザガン</v>
+            <v>イヴィルキング</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>203</v>
+            <v>105</v>
           </cell>
           <cell r="B26" t="str">
-            <v>アスタロト</v>
+            <v>ケルベロス</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>204</v>
+            <v>106</v>
           </cell>
           <cell r="B27" t="str">
-            <v>デカラビア</v>
+            <v>ガルーダ</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>205</v>
+            <v>107</v>
           </cell>
           <cell r="B28" t="str">
-            <v>インドラ</v>
+            <v>ドラゴン</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>206</v>
+            <v>108</v>
           </cell>
           <cell r="B29" t="str">
-            <v>ズルワーン</v>
+            <v>ラミア</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>207</v>
+            <v>109</v>
           </cell>
           <cell r="B30" t="str">
-            <v>アンリマユ</v>
+            <v>コピーパペット</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>301</v>
+            <v>110</v>
           </cell>
           <cell r="B31" t="str">
-            <v>デビルドラゴン</v>
+            <v>ヴァンパイア</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>1001</v>
+            <v>111</v>
           </cell>
           <cell r="B32" t="str">
-            <v>ミカ</v>
+            <v>デス</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>1002</v>
+            <v>112</v>
           </cell>
           <cell r="B33" t="str">
-            <v>エリザベート</v>
+            <v>エナメルスライム</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>1003</v>
+            <v>113</v>
           </cell>
           <cell r="B34" t="str">
-            <v>アリエス</v>
+            <v>デーモン</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>1004</v>
+            <v>114</v>
           </cell>
           <cell r="B35" t="str">
-            <v>シイナ</v>
+            <v>キメラ</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>1005</v>
+            <v>201</v>
           </cell>
           <cell r="B36" t="str">
-            <v>レダ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>1006</v>
+            <v>202</v>
           </cell>
           <cell r="B37" t="str">
-            <v>リシェリ</v>
+            <v>ザガン</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>1007</v>
+            <v>203</v>
           </cell>
           <cell r="B38" t="str">
-            <v>ユニ</v>
+            <v>アスタロト</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>1008</v>
+            <v>204</v>
           </cell>
           <cell r="B39" t="str">
-            <v>マリーベル</v>
+            <v>デカラビア</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>1009</v>
+            <v>205</v>
           </cell>
           <cell r="B40" t="str">
-            <v>ナツキ</v>
+            <v>インドラ</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>1010</v>
+            <v>206</v>
           </cell>
           <cell r="B41" t="str">
-            <v>メリアドール</v>
+            <v>ズルワーン</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
+            <v>207</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>アンリマユ</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>301</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>デビルドラゴン</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1001</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>ミカ</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1002</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>エリザベート</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>1003</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>アリエス</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>1004</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>シイナ</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>1005</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>レダ</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>1006</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>リシェリ</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>1007</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>ユニ</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>1008</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>マリーベル</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>1009</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>ナツキ</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>1010</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>メリアドール</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
             <v>1011</v>
           </cell>
-          <cell r="B42" t="str">
+          <cell r="B54" t="str">
             <v>セリナ</v>
           </cell>
         </row>
@@ -1343,7 +1439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1568,10 +1664,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="B9">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1601,17 +1697,17 @@
         <v>1021</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スライム</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1622,23 +1718,23 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="B11">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C11,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1665,7 +1761,7 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1676,23 +1772,23 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B13">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1719,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1757,23 +1853,23 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="B16">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1800,7 +1896,7 @@
         <v>3</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1811,23 +1907,23 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B18">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>ビー</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1854,7 +1950,7 @@
         <v>3</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1865,23 +1961,23 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="B20">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スペクター</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1908,7 +2004,7 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1919,23 +2015,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B22">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>スケルトン</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1962,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1973,23 +2069,23 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>1101</v>
+        <v>1052</v>
       </c>
       <c r="B24">
-        <v>1101</v>
+        <v>1052</v>
       </c>
       <c r="C24">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>カースド</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2006,17 +2102,17 @@
         <v>1101</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>アモン</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2033,11 +2129,11 @@
         <v>1101</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>ビー</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2054,23 +2150,23 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>2041</v>
+        <v>1101</v>
       </c>
       <c r="B27">
-        <v>2041</v>
+        <v>1101</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スペクター</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -2087,17 +2183,17 @@
         <v>2041</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2114,11 +2210,11 @@
         <v>2041</v>
       </c>
       <c r="C29">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>カースド</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2135,23 +2231,23 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B30">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>スケルトン</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2168,17 +2264,17 @@
         <v>2042</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2195,11 +2291,11 @@
         <v>2042</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>カースド</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -2216,23 +2312,23 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="B33">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="C33">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2249,17 +2345,17 @@
         <v>2101</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ベリト</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2270,23 +2366,23 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B35">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C35">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ウルフ</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2303,17 +2399,17 @@
         <v>2102</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ベリト</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2324,26 +2420,26 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>2201</v>
+        <v>2102</v>
       </c>
       <c r="B37">
-        <v>2201</v>
+        <v>2102</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2357,20 +2453,20 @@
         <v>2201</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2411,11 +2507,11 @@
         <v>2201</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2427,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2438,11 +2534,11 @@
         <v>2201</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2454,34 +2550,34 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B42">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ウルフ</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2492,20 +2588,20 @@
         <v>2202</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2546,11 +2642,11 @@
         <v>2202</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2562,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2573,11 +2669,11 @@
         <v>2202</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2589,34 +2685,34 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B47">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>ビー</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2627,20 +2723,20 @@
         <v>2203</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2681,11 +2777,11 @@
         <v>2203</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スペクター</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2697,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2708,11 +2804,11 @@
         <v>2203</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2724,34 +2820,34 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B52">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>スペクター</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2762,20 +2858,20 @@
         <v>2204</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ビショップ</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2816,11 +2912,11 @@
         <v>2204</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2832,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2843,11 +2939,11 @@
         <v>2204</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ビショップ</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2859,34 +2955,34 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B57">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C57">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2897,20 +2993,20 @@
         <v>2205</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2951,11 +3047,11 @@
         <v>2205</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>カースド</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2967,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2978,11 +3074,11 @@
         <v>2205</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2994,34 +3090,34 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B62">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>カースド</v>
       </c>
       <c r="E62">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3032,20 +3128,20 @@
         <v>3041</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>サイクロプス</v>
+        <v>ビショップ</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3059,11 +3155,11 @@
         <v>3041</v>
       </c>
       <c r="C64">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>サイクロプス</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3086,11 +3182,11 @@
         <v>3041</v>
       </c>
       <c r="C65">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -3107,23 +3203,23 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B66">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ビショップ</v>
       </c>
       <c r="E66">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3140,17 +3236,17 @@
         <v>3042</v>
       </c>
       <c r="C67">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>カースド</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3167,11 +3263,11 @@
         <v>3042</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3194,11 +3290,11 @@
         <v>3042</v>
       </c>
       <c r="C69">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スペクター</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -3215,26 +3311,26 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B70">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="C70">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E70">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -3248,20 +3344,20 @@
         <v>3101</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>パイモン</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -3275,11 +3371,11 @@
         <v>3101</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スライム</v>
       </c>
       <c r="E72">
         <v>5</v>
@@ -3288,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3296,23 +3392,23 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="B73">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="C73">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>クロウ</v>
       </c>
       <c r="E73">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3329,20 +3425,20 @@
         <v>3102</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>パイモン</v>
       </c>
       <c r="E74">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3356,11 +3452,11 @@
         <v>3102</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スライム</v>
       </c>
       <c r="E75">
         <v>15</v>
@@ -3369,40 +3465,40 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" ht="12" customHeight="1" spans="1:8">
+    <row r="76" spans="1:8">
       <c r="A76">
-        <v>4041</v>
-      </c>
-      <c r="B76" s="2">
-        <v>4041</v>
+        <v>3102</v>
+      </c>
+      <c r="B76">
+        <v>3102</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>クロウ</v>
       </c>
       <c r="E76">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" ht="12" customHeight="1" spans="1:8">
       <c r="A77">
         <v>4041</v>
       </c>
@@ -3410,17 +3506,17 @@
         <v>4041</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3464,11 +3560,11 @@
         <v>4041</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>スライム</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3511,27 +3607,27 @@
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="2">
-        <v>4042</v>
+      <c r="A81">
+        <v>4041</v>
       </c>
       <c r="B81" s="2">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E81">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3545,20 +3641,20 @@
         <v>4042</v>
       </c>
       <c r="C82">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>リザード</v>
+        <v>ビー</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3572,11 +3668,11 @@
         <v>4042</v>
       </c>
       <c r="C83">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>リザード</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -3626,11 +3722,11 @@
         <v>4042</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スケルトン</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -3639,31 +3735,31 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86">
-        <v>4101</v>
-      </c>
-      <c r="B86">
-        <v>4101</v>
+      <c r="A86" s="2">
+        <v>4042</v>
+      </c>
+      <c r="B86" s="2">
+        <v>4042</v>
       </c>
       <c r="C86">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ビー</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3674,10 +3770,10 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B87">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="C87">
         <v>104</v>
@@ -3687,7 +3783,7 @@
         <v>アンドラス</v>
       </c>
       <c r="E87">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -3701,20 +3797,20 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B88">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>アンドラス</v>
       </c>
       <c r="E88">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -3741,13 +3837,13 @@
         <v>ブラックナイト</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -3788,11 +3884,11 @@
         <v>5041</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ブラックナイト</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3835,24 +3931,24 @@
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B93" s="2">
-        <v>5042</v>
+      <c r="A93">
+        <v>5041</v>
+      </c>
+      <c r="B93">
+        <v>5041</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スライム</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -3869,20 +3965,20 @@
         <v>5042</v>
       </c>
       <c r="C94">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>ウルフ</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3896,11 +3992,11 @@
         <v>5042</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ビショップ</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -3923,11 +4019,11 @@
         <v>5042</v>
       </c>
       <c r="C96">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E96">
         <v>5</v>
@@ -3936,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -3970,27 +4066,27 @@
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98">
-        <v>5101</v>
-      </c>
-      <c r="B98">
-        <v>5101</v>
+      <c r="A98" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B98" s="2">
+        <v>5042</v>
       </c>
       <c r="C98">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ウルフ</v>
       </c>
       <c r="E98">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4004,20 +4100,20 @@
         <v>5101</v>
       </c>
       <c r="C99">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4031,11 +4127,11 @@
         <v>5101</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E100">
         <v>10</v>
@@ -4058,11 +4154,11 @@
         <v>5101</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スライム</v>
       </c>
       <c r="E101">
         <v>10</v>
@@ -4085,11 +4181,11 @@
         <v>5101</v>
       </c>
       <c r="C102">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E102">
         <v>10</v>
@@ -4106,26 +4202,26 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B103">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C103">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E103">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -4139,20 +4235,20 @@
         <v>5102</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E104">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -4166,11 +4262,11 @@
         <v>5102</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E105">
         <v>20</v>
@@ -4193,11 +4289,11 @@
         <v>5102</v>
       </c>
       <c r="C106">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スライム</v>
       </c>
       <c r="E106">
         <v>20</v>
@@ -4220,11 +4316,11 @@
         <v>5102</v>
       </c>
       <c r="C107">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E107">
         <v>20</v>
@@ -4241,26 +4337,26 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B108">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C108">
-        <v>1002</v>
+        <v>11</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E108">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4274,20 +4370,20 @@
         <v>6021</v>
       </c>
       <c r="C109">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>エリザベート</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4301,11 +4397,11 @@
         <v>6021</v>
       </c>
       <c r="C110">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>アリエス</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4314,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -4328,11 +4424,11 @@
         <v>6021</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>1004</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>シイナ</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4341,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -4355,11 +4451,11 @@
         <v>6021</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>タートルシェル</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4376,23 +4472,23 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B113">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C113">
-        <v>1011</v>
+        <v>1</v>
       </c>
       <c r="D113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>スライム</v>
       </c>
       <c r="E113">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -4409,17 +4505,17 @@
         <v>6022</v>
       </c>
       <c r="C114">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C114,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>セリナ</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -4436,11 +4532,11 @@
         <v>6022</v>
       </c>
       <c r="C115">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C115,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>レダ</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4449,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -4463,11 +4559,11 @@
         <v>6022</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
-        <v>スティングレイ</v>
+        <v>メリアドール</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4490,11 +4586,11 @@
         <v>6022</v>
       </c>
       <c r="C117">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スティングレイ</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4503,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -4511,23 +4607,23 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B118">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C118">
-        <v>1001</v>
+        <v>14</v>
       </c>
       <c r="D118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C118,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E118">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -4544,17 +4640,17 @@
         <v>6031</v>
       </c>
       <c r="C119">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="D119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C119,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ミカ</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -4571,11 +4667,11 @@
         <v>6031</v>
       </c>
       <c r="C120">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C120,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>リシェリ</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4598,11 +4694,11 @@
         <v>6031</v>
       </c>
       <c r="C121">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C121,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4625,11 +4721,11 @@
         <v>6031</v>
       </c>
       <c r="C122">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C122,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>ユニ</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4646,26 +4742,26 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B123">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C123">
-        <v>201</v>
+        <v>1009</v>
       </c>
       <c r="D123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C123,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E123">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -4679,20 +4775,20 @@
         <v>6101</v>
       </c>
       <c r="C124">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="D124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C124,[1]TextData!A:A))</f>
-        <v>リザード</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -4706,11 +4802,11 @@
         <v>6101</v>
       </c>
       <c r="C125">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>リザード</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4733,11 +4829,11 @@
         <v>6101</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C126,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>フィッシャーマン</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4746,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -4760,22 +4856,49 @@
         <v>6101</v>
       </c>
       <c r="C127">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C127,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128">
+        <v>6101</v>
+      </c>
+      <c r="B128">
+        <v>6101</v>
+      </c>
+      <c r="C128">
+        <v>13</v>
+      </c>
+      <c r="D128" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C128,[1]TextData!A:A))</f>
         <v>サイクロプス</v>
       </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-      <c r="F127">
-        <v>0</v>
-      </c>
-      <c r="G127">
-        <v>1</v>
-      </c>
-      <c r="H127">
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,9 +48,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -76,9 +76,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -92,8 +107,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,11 +122,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -130,31 +177,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,39 +191,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,7 +215,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,175 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,6 +418,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -429,6 +444,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -457,6 +481,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -471,41 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D2" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C2,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E2">
         <v>40</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D3" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C3,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="D4" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C4,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E4">
         <v>40</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D5" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C5,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D6" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C6,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="D7" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C7,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D8" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C8,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1680,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="D11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C11,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C12,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ベヒーモス</v>
       </c>
       <c r="E25">
         <v>10</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E31">
         <v>15</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E34">
         <v>10</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E36">
         <v>20</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E37">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E48">
         <v>5</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E53">
         <v>5</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E63">
         <v>5</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>サイクロプス</v>
+        <v>オーク</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>バット</v>
       </c>
       <c r="E67">
         <v>15</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>スペクター</v>
+        <v>スネーク</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E70">
         <v>5</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>シルフ</v>
       </c>
       <c r="E71">
         <v>15</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E73">
         <v>5</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>シルフ</v>
       </c>
       <c r="E74">
         <v>25</v>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E76">
         <v>15</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E77">
         <v>5</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E82">
         <v>15</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>リザード</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E86">
         <v>5</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E87">
         <v>20</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E88">
         <v>30</v>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E89">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>ブラックナイト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E94">
         <v>15</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>ビショップ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E96">
         <v>5</v>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E97">
         <v>5</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E98">
         <v>5</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E99">
         <v>30</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E100">
         <v>10</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E102">
         <v>10</v>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E103">
         <v>10</v>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E104">
         <v>40</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E105">
         <v>20</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E107">
         <v>20</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E108">
         <v>20</v>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>タートルシェル</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
-        <v>スティングレイ</v>
+        <v>マッドプラント</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C118,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
-        <v>リザード</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="D126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C126,[1]TextData!A:A))</f>
-        <v>フィッシャーマン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C127,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C128,[1]TextData!A:A))</f>
-        <v>サイクロプス</v>
+        <v>オーク</v>
       </c>
       <c r="E128">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="6620"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,8 +48,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -59,6 +59,60 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -76,24 +130,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -109,91 +193,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,7 +215,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,169 +389,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,6 +418,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -433,17 +448,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -451,8 +460,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -472,11 +481,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,21 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -535,124 +535,124 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1439,7 +1439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1691,23 +1691,23 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="B10">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スパイダー</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1718,23 +1718,23 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="B11">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C11,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>インプ</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1745,23 +1745,23 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B12">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C12,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>インプ</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1772,20 +1772,20 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B13">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>インプ</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1799,20 +1799,20 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="B14">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="C14">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ホーネット</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1826,20 +1826,20 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="B15">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ホーネット</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1853,23 +1853,23 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="B16">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スネーク</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1880,23 +1880,23 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B17">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スネーク</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1907,23 +1907,23 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="B18">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>インプ</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1934,23 +1934,23 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="B19">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>インプ</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1961,23 +1961,23 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>1042</v>
+        <v>1052</v>
       </c>
       <c r="B20">
-        <v>1042</v>
+        <v>1052</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>バット</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1988,23 +1988,23 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B21">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>バット</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2015,23 +2015,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>1051</v>
+        <v>1101</v>
       </c>
       <c r="B22">
-        <v>1051</v>
+        <v>1101</v>
       </c>
       <c r="C22">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ベヒーモス</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2042,23 +2042,23 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>1052</v>
+        <v>1101</v>
       </c>
       <c r="B23">
-        <v>1052</v>
+        <v>1101</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ホーネット</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2069,20 +2069,20 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>1052</v>
+        <v>1101</v>
       </c>
       <c r="B24">
-        <v>1052</v>
+        <v>1101</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スネーク</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2096,20 +2096,20 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="B25">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="C25">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>ベヒーモス</v>
+        <v>スパイダー</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2123,20 +2123,20 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="B26">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>バット</v>
       </c>
       <c r="E26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2150,20 +2150,20 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="B27">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>インプ</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2177,20 +2177,20 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B28">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ゴースト</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B29">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -2217,7 +2217,7 @@
         <v>バット</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B30">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C30">
         <v>14</v>
@@ -2244,7 +2244,7 @@
         <v>インプ</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2258,20 +2258,20 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="B31">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2285,20 +2285,20 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="B32">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スパイダー</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2312,23 +2312,23 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2042</v>
+        <v>2102</v>
       </c>
       <c r="B33">
-        <v>2042</v>
+        <v>2102</v>
       </c>
       <c r="C33">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2339,23 +2339,23 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B34">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="C34">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>スパイダー</v>
       </c>
       <c r="E34">
         <v>10</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2366,26 +2366,26 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="B35">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2393,23 +2393,23 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>2102</v>
+        <v>2201</v>
       </c>
       <c r="B36">
-        <v>2102</v>
+        <v>2201</v>
       </c>
       <c r="C36">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>スパイダー</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>2102</v>
+        <v>2201</v>
       </c>
       <c r="B37">
-        <v>2102</v>
+        <v>2201</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -2433,7 +2433,7 @@
         <v>スパイダー</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2460,16 +2460,16 @@
         <v>ゼリーフィッシュ</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2496,31 +2496,31 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B40">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2528,17 +2528,17 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B41">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>ホーネット</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2550,22 +2550,22 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B42">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2595,16 +2595,16 @@
         <v>ビッグラット</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2631,31 +2631,31 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B45">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2663,17 +2663,17 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B46">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>スネーク</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2685,22 +2685,22 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B47">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スネーク</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2730,16 +2730,16 @@
         <v>スコーピオン</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2766,31 +2766,31 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B50">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -2798,17 +2798,17 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B51">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>インプ</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2820,22 +2820,22 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B52">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>インプ</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2865,16 +2865,16 @@
         <v>ウィスプ</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2901,31 +2901,31 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B55">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C55">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2933,17 +2933,17 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B56">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>バット</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2955,22 +2955,22 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B57">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C57">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>バット</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3000,16 +3000,16 @@
         <v>スケルトン</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3036,31 +3036,31 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B60">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3068,17 +3068,17 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B61">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C61">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>オーク</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3090,22 +3090,22 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B62">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>インプ</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3135,13 +3135,13 @@
         <v>ウィスプ</v>
       </c>
       <c r="E63">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3149,23 +3149,23 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B64">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C64">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>オーク</v>
+        <v>バット</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3176,20 +3176,20 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B65">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C65">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3203,20 +3203,20 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B66">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>スネーク</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3236,17 +3236,17 @@
         <v>3042</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スケルトン</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3257,26 +3257,26 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B68">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="C68">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>シルフ</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3284,17 +3284,17 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B69">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スライム</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -3311,17 +3311,17 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B70">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="C70">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E70">
         <v>5</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="B71">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="C71">
         <v>103</v>
@@ -3351,7 +3351,7 @@
         <v>シルフ</v>
       </c>
       <c r="E71">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="B72">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3378,7 +3378,7 @@
         <v>スライム</v>
       </c>
       <c r="E72">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="B73">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -3405,7 +3405,7 @@
         <v>ビッグラット</v>
       </c>
       <c r="E73">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -3417,28 +3417,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" ht="12" customHeight="1" spans="1:8">
       <c r="A74">
-        <v>3102</v>
-      </c>
-      <c r="B74">
-        <v>3102</v>
+        <v>4041</v>
+      </c>
+      <c r="B74" s="2">
+        <v>4041</v>
       </c>
       <c r="C74">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E74">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>3102</v>
-      </c>
-      <c r="B75">
-        <v>3102</v>
+        <v>4041</v>
+      </c>
+      <c r="B75" s="2">
+        <v>4041</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3459,7 +3459,7 @@
         <v>スライム</v>
       </c>
       <c r="E75">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3473,32 +3473,32 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>3102</v>
-      </c>
-      <c r="B76">
-        <v>3102</v>
+        <v>4041</v>
+      </c>
+      <c r="B76" s="2">
+        <v>4041</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>スライム</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" ht="12" customHeight="1" spans="1:8">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>4041</v>
       </c>
@@ -3506,17 +3506,17 @@
         <v>4041</v>
       </c>
       <c r="C77">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3533,11 +3533,11 @@
         <v>4041</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ゴースト</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3553,48 +3553,48 @@
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79">
-        <v>4041</v>
+      <c r="A79" s="2">
+        <v>4042</v>
       </c>
       <c r="B79" s="2">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ホーネット</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80">
-        <v>4041</v>
+      <c r="A80" s="2">
+        <v>4042</v>
       </c>
       <c r="B80" s="2">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C80">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3607,21 +3607,21 @@
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81">
-        <v>4041</v>
+      <c r="A81" s="2">
+        <v>4042</v>
       </c>
       <c r="B81" s="2">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C81">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>インプ</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3641,20 +3641,20 @@
         <v>4042</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>インプ</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3668,11 +3668,11 @@
         <v>4042</v>
       </c>
       <c r="C83">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -3681,85 +3681,85 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B84" s="2">
-        <v>4042</v>
+      <c r="A84">
+        <v>4101</v>
+      </c>
+      <c r="B84">
+        <v>4101</v>
       </c>
       <c r="C84">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E84">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B85" s="2">
-        <v>4042</v>
+      <c r="A85">
+        <v>4102</v>
+      </c>
+      <c r="B85">
+        <v>4102</v>
       </c>
       <c r="C85">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B86" s="2">
-        <v>4042</v>
+      <c r="A86">
+        <v>5041</v>
+      </c>
+      <c r="B86">
+        <v>5041</v>
       </c>
       <c r="C86">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スケルトン</v>
       </c>
       <c r="E86">
         <v>5</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3770,26 +3770,26 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>4101</v>
+        <v>5041</v>
       </c>
       <c r="B87">
-        <v>4101</v>
+        <v>5041</v>
       </c>
       <c r="C87">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>スケルトン</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3797,26 +3797,26 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="B88">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="C88">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>スケルトン</v>
       </c>
       <c r="E88">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -3830,20 +3830,20 @@
         <v>5041</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スライム</v>
       </c>
       <c r="E89">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -3857,11 +3857,11 @@
         <v>5041</v>
       </c>
       <c r="C90">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スライム</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3877,24 +3877,24 @@
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91">
-        <v>5041</v>
-      </c>
-      <c r="B91">
-        <v>5041</v>
+      <c r="A91" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B91" s="2">
+        <v>5042</v>
       </c>
       <c r="C91">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スパイダー</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -3904,54 +3904,54 @@
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92">
-        <v>5041</v>
-      </c>
-      <c r="B92">
-        <v>5041</v>
+      <c r="A92" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B92" s="2">
+        <v>5042</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F92">
         <v>0</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93">
-        <v>5041</v>
-      </c>
-      <c r="B93">
-        <v>5041</v>
+      <c r="A93" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B93" s="2">
+        <v>5042</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>インプ</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3972,10 +3972,10 @@
         <v>スパイダー</v>
       </c>
       <c r="E94">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -3992,11 +3992,11 @@
         <v>5042</v>
       </c>
       <c r="C95">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -4005,31 +4005,31 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B96" s="2">
-        <v>5042</v>
+      <c r="A96">
+        <v>5101</v>
+      </c>
+      <c r="B96">
+        <v>5101</v>
       </c>
       <c r="C96">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -4039,21 +4039,21 @@
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B97" s="2">
-        <v>5042</v>
+      <c r="A97">
+        <v>5101</v>
+      </c>
+      <c r="B97">
+        <v>5101</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -4066,21 +4066,21 @@
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B98" s="2">
-        <v>5042</v>
+      <c r="A98">
+        <v>5101</v>
+      </c>
+      <c r="B98">
+        <v>5101</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スライム</v>
       </c>
       <c r="E98">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -4100,20 +4100,20 @@
         <v>5101</v>
       </c>
       <c r="C99">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E99">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4127,11 +4127,11 @@
         <v>5101</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E100">
         <v>10</v>
@@ -4148,26 +4148,26 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B101">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -4175,10 +4175,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B102">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C102">
         <v>8</v>
@@ -4188,7 +4188,7 @@
         <v>スコーピオン</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4202,20 +4202,20 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B103">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C103">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スライム</v>
       </c>
       <c r="E103">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4235,20 +4235,20 @@
         <v>5102</v>
       </c>
       <c r="C104">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E104">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -4262,11 +4262,11 @@
         <v>5102</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴースト</v>
       </c>
       <c r="E105">
         <v>20</v>
@@ -4283,26 +4283,26 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B106">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>エリザベート</v>
       </c>
       <c r="E106">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4310,20 +4310,20 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B107">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>1003</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>アリエス</v>
       </c>
       <c r="E107">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -4337,26 +4337,26 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B108">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C108">
-        <v>11</v>
+        <v>1004</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>シイナ</v>
       </c>
       <c r="E108">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>0</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4370,20 +4370,20 @@
         <v>6021</v>
       </c>
       <c r="C109">
-        <v>1002</v>
+        <v>8</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4397,11 +4397,11 @@
         <v>6021</v>
       </c>
       <c r="C110">
-        <v>1003</v>
+        <v>1</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>スライム</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4418,26 +4418,26 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B111">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C111">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>セリナ</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -4445,17 +4445,17 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B112">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>1005</v>
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>レダ</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4472,17 +4472,17 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B113">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="D113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>メリアドール</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -4505,20 +4505,20 @@
         <v>6022</v>
       </c>
       <c r="C114">
-        <v>1011</v>
+        <v>10</v>
       </c>
       <c r="D114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C114,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>マッドプラント</v>
       </c>
       <c r="E114">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -4532,11 +4532,11 @@
         <v>6022</v>
       </c>
       <c r="C115">
-        <v>1005</v>
+        <v>14</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C115,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>インプ</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4553,26 +4553,26 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B116">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C116">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>ミカ</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -4580,17 +4580,17 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B117">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C117">
-        <v>10</v>
+        <v>1006</v>
       </c>
       <c r="D117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
-        <v>マッドプラント</v>
+        <v>リシェリ</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -4607,17 +4607,17 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B118">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C118">
-        <v>14</v>
+        <v>1008</v>
       </c>
       <c r="D118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C118,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4640,17 +4640,17 @@
         <v>6031</v>
       </c>
       <c r="C119">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C119,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>ユニ</v>
       </c>
       <c r="E119">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -4667,11 +4667,11 @@
         <v>6031</v>
       </c>
       <c r="C120">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C120,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4688,26 +4688,26 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B121">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C121">
-        <v>1008</v>
+        <v>201</v>
       </c>
       <c r="D121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C121,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -4715,17 +4715,17 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B122">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C122">
-        <v>1007</v>
+        <v>15</v>
       </c>
       <c r="D122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C122,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4742,17 +4742,17 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B123">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C123">
-        <v>1009</v>
+        <v>11</v>
       </c>
       <c r="D123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C123,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>ゴースト</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4775,17 +4775,17 @@
         <v>6101</v>
       </c>
       <c r="C124">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="D124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C124,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E124">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -4802,11 +4802,11 @@
         <v>6101</v>
       </c>
       <c r="C125">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>オーク</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4815,90 +4815,9 @@
         <v>0</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126">
-        <v>6101</v>
-      </c>
-      <c r="B126">
-        <v>6101</v>
-      </c>
-      <c r="C126">
-        <v>11</v>
-      </c>
-      <c r="D126" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C126,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-      <c r="F126">
-        <v>0</v>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127">
-        <v>6101</v>
-      </c>
-      <c r="B127">
-        <v>6101</v>
-      </c>
-      <c r="C127">
-        <v>5</v>
-      </c>
-      <c r="D127" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C127,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-      <c r="F127">
-        <v>0</v>
-      </c>
-      <c r="G127">
-        <v>1</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128">
-        <v>6101</v>
-      </c>
-      <c r="B128">
-        <v>6101</v>
-      </c>
-      <c r="C128">
-        <v>13</v>
-      </c>
-      <c r="D128" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C128,[1]TextData!A:A))</f>
-        <v>オーク</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-      <c r="F128">
-        <v>0</v>
-      </c>
-      <c r="G128">
-        <v>1</v>
-      </c>
-      <c r="H128">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,38 +63,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -109,8 +86,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -123,8 +116,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,7 +146,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -154,7 +177,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,9 +190,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -177,30 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,13 +215,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,25 +269,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,13 +293,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,13 +323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,49 +341,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,13 +371,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,19 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -433,35 +442,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,16 +472,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1439,7 +1439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1697,14 +1697,14 @@
         <v>1031</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スライム</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1718,23 +1718,23 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="B11">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C11,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スライム</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1745,23 +1745,23 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="B12">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C12,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スライム</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1772,23 +1772,23 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="B13">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スライム</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1799,23 +1799,23 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="B14">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スライム</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1826,23 +1826,23 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1041</v>
+        <v>1101</v>
       </c>
       <c r="B15">
-        <v>1041</v>
+        <v>1101</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ベヒーモス</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1853,20 +1853,20 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>1042</v>
+        <v>2041</v>
       </c>
       <c r="B16">
-        <v>1042</v>
+        <v>2041</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スパイダー</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1880,20 +1880,20 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>1042</v>
+        <v>2041</v>
       </c>
       <c r="B17">
-        <v>1042</v>
+        <v>2041</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>バット</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>1051</v>
+        <v>2041</v>
       </c>
       <c r="B18">
-        <v>1051</v>
+        <v>2041</v>
       </c>
       <c r="C18">
         <v>14</v>
@@ -1920,10 +1920,10 @@
         <v>インプ</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1934,23 +1934,23 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>1051</v>
+        <v>2042</v>
       </c>
       <c r="B19">
-        <v>1051</v>
+        <v>2042</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゴースト</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>1052</v>
+        <v>2042</v>
       </c>
       <c r="B20">
-        <v>1052</v>
+        <v>2042</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1974,10 +1974,10 @@
         <v>バット</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1988,20 +1988,20 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>1052</v>
+        <v>2042</v>
       </c>
       <c r="B21">
-        <v>1052</v>
+        <v>2042</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>インプ</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2015,17 +2015,17 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>1101</v>
+        <v>2101</v>
       </c>
       <c r="B22">
-        <v>1101</v>
+        <v>2101</v>
       </c>
       <c r="C22">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ベヒーモス</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -2042,20 +2042,20 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>1101</v>
+        <v>2101</v>
       </c>
       <c r="B23">
-        <v>1101</v>
+        <v>2101</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スパイダー</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2069,23 +2069,23 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>1101</v>
+        <v>2102</v>
       </c>
       <c r="B24">
-        <v>1101</v>
+        <v>2102</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>2041</v>
+        <v>2102</v>
       </c>
       <c r="B25">
-        <v>2041</v>
+        <v>2102</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -2109,10 +2109,10 @@
         <v>スパイダー</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2123,26 +2123,26 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="B26">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2150,17 +2150,17 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="B27">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="C27">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2177,23 +2177,23 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="B28">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スパイダー</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2204,20 +2204,20 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="B29">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2226,25 +2226,25 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="B30">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="C30">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2253,31 +2253,31 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>2101</v>
+        <v>2202</v>
       </c>
       <c r="B31">
-        <v>2101</v>
+        <v>2202</v>
       </c>
       <c r="C31">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2285,17 +2285,17 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>2101</v>
+        <v>2202</v>
       </c>
       <c r="B32">
-        <v>2101</v>
+        <v>2202</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2312,23 +2312,23 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2102</v>
+        <v>2202</v>
       </c>
       <c r="B33">
-        <v>2102</v>
+        <v>2202</v>
       </c>
       <c r="C33">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>ホーネット</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2339,20 +2339,20 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>2102</v>
+        <v>2202</v>
       </c>
       <c r="B34">
-        <v>2102</v>
+        <v>2202</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2361,58 +2361,58 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B35">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>ホーネット</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B36">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2420,17 +2420,17 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B37">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スネーク</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2447,17 +2447,17 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B38">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>スネーク</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2469,22 +2469,22 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B39">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2496,58 +2496,58 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B40">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>スネーク</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B41">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2555,17 +2555,17 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B42">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>インプ</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2582,17 +2582,17 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B43">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>インプ</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2604,22 +2604,22 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B44">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2631,58 +2631,58 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B45">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>インプ</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B46">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スケルトン</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2690,17 +2690,17 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B47">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>バット</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2717,17 +2717,17 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B48">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>バット</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2739,22 +2739,22 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B49">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スケルトン</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2766,58 +2766,58 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B50">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>バット</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="B51">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -2825,17 +2825,17 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="B52">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="C52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>オーク</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2852,17 +2852,17 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="B53">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>インプ</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2874,22 +2874,22 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="B54">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="C54">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2901,31 +2901,31 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="B55">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>バット</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2933,20 +2933,20 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="B56">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スケルトン</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2960,20 +2960,20 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="B57">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スネーク</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="B58">
-        <v>2205</v>
+        <v>3042</v>
       </c>
       <c r="C58">
         <v>12</v>
@@ -3000,7 +3000,7 @@
         <v>スケルトン</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3009,58 +3009,58 @@
         <v>0</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>2205</v>
+        <v>3101</v>
       </c>
       <c r="B59">
-        <v>2205</v>
+        <v>3101</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>シルフ</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>3041</v>
+        <v>3101</v>
       </c>
       <c r="B60">
-        <v>3041</v>
+        <v>3101</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>スライム</v>
       </c>
       <c r="E60">
         <v>5</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3068,26 +3068,26 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>3041</v>
+        <v>3101</v>
       </c>
       <c r="B61">
-        <v>3041</v>
+        <v>3101</v>
       </c>
       <c r="C61">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>オーク</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3095,26 +3095,26 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>3041</v>
+        <v>3102</v>
       </c>
       <c r="B62">
-        <v>3041</v>
+        <v>3102</v>
       </c>
       <c r="C62">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シルフ</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -3122,20 +3122,20 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>3041</v>
+        <v>3102</v>
       </c>
       <c r="B63">
-        <v>3041</v>
+        <v>3102</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>スライム</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3149,50 +3149,50 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>3042</v>
+        <v>3102</v>
       </c>
       <c r="B64">
-        <v>3042</v>
+        <v>3102</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E64">
         <v>15</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" ht="12" customHeight="1" spans="1:8">
       <c r="A65">
-        <v>3042</v>
-      </c>
-      <c r="B65">
-        <v>3042</v>
+        <v>4041</v>
+      </c>
+      <c r="B65" s="2">
+        <v>4041</v>
       </c>
       <c r="C65">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E65">
         <v>5</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3203,20 +3203,20 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>3042</v>
-      </c>
-      <c r="B66">
-        <v>3042</v>
+        <v>4041</v>
+      </c>
+      <c r="B66" s="2">
+        <v>4041</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スライム</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3230,20 +3230,20 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>3042</v>
-      </c>
-      <c r="B67">
-        <v>3042</v>
+        <v>4041</v>
+      </c>
+      <c r="B67" s="2">
+        <v>4041</v>
       </c>
       <c r="C67">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スライム</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3257,26 +3257,26 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>3101</v>
-      </c>
-      <c r="B68">
-        <v>3101</v>
+        <v>4041</v>
+      </c>
+      <c r="B68" s="2">
+        <v>4041</v>
       </c>
       <c r="C68">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>ゴースト</v>
       </c>
       <c r="E68">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3284,20 +3284,20 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>3101</v>
-      </c>
-      <c r="B69">
-        <v>3101</v>
+        <v>4041</v>
+      </c>
+      <c r="B69" s="2">
+        <v>4041</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ゴースト</v>
       </c>
       <c r="E69">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3310,24 +3310,24 @@
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70">
-        <v>3101</v>
-      </c>
-      <c r="B70">
-        <v>3101</v>
+      <c r="A70" s="2">
+        <v>4042</v>
+      </c>
+      <c r="B70" s="2">
+        <v>4042</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>ホーネット</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3337,48 +3337,48 @@
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71">
-        <v>3102</v>
-      </c>
-      <c r="B71">
-        <v>3102</v>
+      <c r="A71" s="2">
+        <v>4042</v>
+      </c>
+      <c r="B71" s="2">
+        <v>4042</v>
       </c>
       <c r="C71">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E71">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72">
-        <v>3102</v>
-      </c>
-      <c r="B72">
-        <v>3102</v>
+      <c r="A72" s="2">
+        <v>4042</v>
+      </c>
+      <c r="B72" s="2">
+        <v>4042</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>インプ</v>
       </c>
       <c r="E72">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3391,54 +3391,54 @@
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73">
-        <v>3102</v>
-      </c>
-      <c r="B73">
-        <v>3102</v>
+      <c r="A73" s="2">
+        <v>4042</v>
+      </c>
+      <c r="B73" s="2">
+        <v>4042</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>インプ</v>
       </c>
       <c r="E73">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" ht="12" customHeight="1" spans="1:8">
-      <c r="A74">
-        <v>4041</v>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2">
+        <v>4042</v>
       </c>
       <c r="B74" s="2">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ホーネット</v>
       </c>
       <c r="E74">
         <v>5</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3446,26 +3446,26 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>4041</v>
-      </c>
-      <c r="B75" s="2">
-        <v>4041</v>
+        <v>4101</v>
+      </c>
+      <c r="B75">
+        <v>4101</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3473,26 +3473,26 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>4041</v>
-      </c>
-      <c r="B76" s="2">
-        <v>4041</v>
+        <v>4102</v>
+      </c>
+      <c r="B76">
+        <v>4102</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3500,26 +3500,26 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>4041</v>
-      </c>
-      <c r="B77" s="2">
-        <v>4041</v>
+        <v>5041</v>
+      </c>
+      <c r="B77">
+        <v>5041</v>
       </c>
       <c r="C77">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3527,17 +3527,17 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>4041</v>
-      </c>
-      <c r="B78" s="2">
-        <v>4041</v>
+        <v>5041</v>
+      </c>
+      <c r="B78">
+        <v>5041</v>
       </c>
       <c r="C78">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スケルトン</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3553,48 +3553,48 @@
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B79" s="2">
-        <v>4042</v>
+      <c r="A79">
+        <v>5041</v>
+      </c>
+      <c r="B79">
+        <v>5041</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>スケルトン</v>
       </c>
       <c r="E79">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B80" s="2">
-        <v>4042</v>
+      <c r="A80">
+        <v>5041</v>
+      </c>
+      <c r="B80">
+        <v>5041</v>
       </c>
       <c r="C80">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>スライム</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3607,21 +3607,21 @@
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B81" s="2">
-        <v>4042</v>
+      <c r="A81">
+        <v>5041</v>
+      </c>
+      <c r="B81">
+        <v>5041</v>
       </c>
       <c r="C81">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スライム</v>
       </c>
       <c r="E81">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3635,23 +3635,23 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="B82" s="2">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="C82">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -3662,17 +3662,17 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="B83" s="2">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -3688,24 +3688,24 @@
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84">
-        <v>4101</v>
-      </c>
-      <c r="B84">
-        <v>4101</v>
+      <c r="A84" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B84" s="2">
+        <v>5042</v>
       </c>
       <c r="C84">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>インプ</v>
       </c>
       <c r="E84">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3715,54 +3715,54 @@
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85">
-        <v>4102</v>
-      </c>
-      <c r="B85">
-        <v>4102</v>
+      <c r="A85" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B85" s="2">
+        <v>5042</v>
       </c>
       <c r="C85">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>スパイダー</v>
       </c>
       <c r="E85">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86">
-        <v>5041</v>
-      </c>
-      <c r="B86">
-        <v>5041</v>
+      <c r="A86" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B86" s="2">
+        <v>5042</v>
       </c>
       <c r="C86">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スパイダー</v>
       </c>
       <c r="E86">
         <v>5</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -3770,26 +3770,26 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="B87">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3797,20 +3797,20 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="B88">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="B89">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>スライム</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3851,20 +3851,20 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="B90">
-        <v>5041</v>
+        <v>5101</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -3877,24 +3877,24 @@
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B91" s="2">
-        <v>5042</v>
+      <c r="A91">
+        <v>5101</v>
+      </c>
+      <c r="B91">
+        <v>5101</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ゴースト</v>
       </c>
       <c r="E91">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -3904,24 +3904,24 @@
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B92" s="2">
-        <v>5042</v>
+      <c r="A92">
+        <v>5102</v>
+      </c>
+      <c r="B92">
+        <v>5102</v>
       </c>
       <c r="C92">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E92">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3931,48 +3931,48 @@
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B93" s="2">
-        <v>5042</v>
+      <c r="A93">
+        <v>5102</v>
+      </c>
+      <c r="B93">
+        <v>5102</v>
       </c>
       <c r="C93">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E93">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B94" s="2">
-        <v>5042</v>
+      <c r="A94">
+        <v>5102</v>
+      </c>
+      <c r="B94">
+        <v>5102</v>
       </c>
       <c r="C94">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スライム</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -3985,21 +3985,21 @@
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B95" s="2">
-        <v>5042</v>
+      <c r="A95">
+        <v>5102</v>
+      </c>
+      <c r="B95">
+        <v>5102</v>
       </c>
       <c r="C95">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4013,26 +4013,26 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B96">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C96">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>ゴースト</v>
       </c>
       <c r="E96">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -4040,26 +4040,26 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="B97">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="C97">
-        <v>8</v>
+        <v>1002</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>エリザベート</v>
       </c>
       <c r="E97">
         <v>10</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -4067,20 +4067,20 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="B98">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>アリエス</v>
       </c>
       <c r="E98">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -4094,26 +4094,26 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="B99">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="C99">
-        <v>8</v>
+        <v>1004</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>シイナ</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4121,20 +4121,20 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="B100">
-        <v>5101</v>
+        <v>6021</v>
       </c>
       <c r="C100">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E100">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -4148,26 +4148,26 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B101">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C101">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>スライム</v>
       </c>
       <c r="E101">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -4175,23 +4175,23 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="B102">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>1011</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>セリナ</v>
       </c>
       <c r="E102">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4202,20 +4202,20 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="B103">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>1005</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>レダ</v>
       </c>
       <c r="E103">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4229,26 +4229,26 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="B104">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>1010</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>メリアドール</v>
       </c>
       <c r="E104">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -4256,26 +4256,26 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="B105">
-        <v>5102</v>
+        <v>6022</v>
       </c>
       <c r="C105">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>マッドプラント</v>
       </c>
       <c r="E105">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>0</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -4283,26 +4283,26 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B106">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C106">
-        <v>1002</v>
+        <v>14</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>インプ</v>
       </c>
       <c r="E106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4310,23 +4310,23 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="B107">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="C107">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>ミカ</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -4337,17 +4337,17 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="B108">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="C108">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>リシェリ</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4356,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4364,17 +4364,17 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="B109">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="C109">
-        <v>8</v>
+        <v>1008</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>マリーベル</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4391,17 +4391,17 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="B110">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>1007</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ユニ</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4418,23 +4418,23 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B111">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C111">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E111">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -4445,26 +4445,26 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="B112">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="C112">
-        <v>1005</v>
+        <v>201</v>
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4472,17 +4472,17 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="B113">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="C113">
-        <v>1010</v>
+        <v>15</v>
       </c>
       <c r="D113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -4499,17 +4499,17 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="B114">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="C114">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C114,[1]TextData!A:A))</f>
-        <v>マッドプラント</v>
+        <v>ゴースト</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -4526,17 +4526,17 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="B115">
-        <v>6022</v>
+        <v>6101</v>
       </c>
       <c r="C115">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C115,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -4553,271 +4553,28 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B116">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C116">
-        <v>1001</v>
+        <v>13</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>オーク</v>
       </c>
       <c r="E116">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117">
-        <v>6031</v>
-      </c>
-      <c r="B117">
-        <v>6031</v>
-      </c>
-      <c r="C117">
-        <v>1006</v>
-      </c>
-      <c r="D117" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117">
-        <v>0</v>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118">
-        <v>6031</v>
-      </c>
-      <c r="B118">
-        <v>6031</v>
-      </c>
-      <c r="C118">
-        <v>1008</v>
-      </c>
-      <c r="D118" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C118,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118">
-        <v>0</v>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119">
-        <v>6031</v>
-      </c>
-      <c r="B119">
-        <v>6031</v>
-      </c>
-      <c r="C119">
-        <v>1007</v>
-      </c>
-      <c r="D119" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C119,[1]TextData!A:A))</f>
-        <v>ユニ</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120">
-        <v>6031</v>
-      </c>
-      <c r="B120">
-        <v>6031</v>
-      </c>
-      <c r="C120">
-        <v>1009</v>
-      </c>
-      <c r="D120" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C120,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-      <c r="F120">
-        <v>0</v>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121">
-        <v>6101</v>
-      </c>
-      <c r="B121">
-        <v>6101</v>
-      </c>
-      <c r="C121">
-        <v>201</v>
-      </c>
-      <c r="D121" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C121,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
-      </c>
-      <c r="E121">
-        <v>10</v>
-      </c>
-      <c r="F121">
-        <v>1</v>
-      </c>
-      <c r="G121">
-        <v>1</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122">
-        <v>6101</v>
-      </c>
-      <c r="B122">
-        <v>6101</v>
-      </c>
-      <c r="C122">
-        <v>15</v>
-      </c>
-      <c r="D122" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C122,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
-      </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-      <c r="F122">
-        <v>0</v>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123">
-        <v>6101</v>
-      </c>
-      <c r="B123">
-        <v>6101</v>
-      </c>
-      <c r="C123">
-        <v>11</v>
-      </c>
-      <c r="D123" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C123,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
-      </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
-      <c r="F123">
-        <v>0</v>
-      </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124">
-        <v>6101</v>
-      </c>
-      <c r="B124">
-        <v>6101</v>
-      </c>
-      <c r="C124">
-        <v>5</v>
-      </c>
-      <c r="D124" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C124,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
-      </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
-      <c r="F124">
-        <v>0</v>
-      </c>
-      <c r="G124">
-        <v>1</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125">
-        <v>6101</v>
-      </c>
-      <c r="B125">
-        <v>6101</v>
-      </c>
-      <c r="C125">
-        <v>13</v>
-      </c>
-      <c r="D125" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
-        <v>オーク</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-      <c r="F125">
-        <v>0</v>
-      </c>
-      <c r="G125">
-        <v>1</v>
-      </c>
-      <c r="H125">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -62,27 +62,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -94,16 +77,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -124,8 +107,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -139,17 +167,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -161,46 +183,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,6 +212,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -227,13 +233,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,7 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,43 +365,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,97 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,24 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -443,6 +425,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -453,21 +450,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,6 +480,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1439,7 +1439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1697,11 +1697,11 @@
         <v>1031</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ホーネット</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1761,7 +1761,7 @@
         <v>4</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1772,23 +1772,23 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B13">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ホーネット</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1826,20 +1826,20 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="B15">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C15">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ベヒーモス</v>
+        <v>ホーネット</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1853,20 +1853,20 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>2041</v>
+        <v>1101</v>
       </c>
       <c r="B16">
-        <v>2041</v>
+        <v>1101</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ベヒーモス</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1886,17 +1886,17 @@
         <v>2041</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スパイダー</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1913,11 +1913,11 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>バット</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1934,23 +1934,23 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B19">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>インプ</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1967,17 +1967,17 @@
         <v>2042</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ゴースト</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1994,11 +1994,11 @@
         <v>2042</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>バット</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -2015,23 +2015,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="B22">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="C22">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>インプ</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2048,17 +2048,17 @@
         <v>2101</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2069,23 +2069,23 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B24">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C24">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>スパイダー</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2102,17 +2102,17 @@
         <v>2102</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ミノタウロス</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2123,26 +2123,26 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>2201</v>
+        <v>2102</v>
       </c>
       <c r="B26">
-        <v>2201</v>
+        <v>2102</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2156,20 +2156,20 @@
         <v>2201</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2210,11 +2210,11 @@
         <v>2201</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2237,11 +2237,11 @@
         <v>2201</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ゼリーフィッシュ</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2253,34 +2253,34 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B31">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>スパイダー</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2291,20 +2291,20 @@
         <v>2202</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2345,11 +2345,11 @@
         <v>2202</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>ホーネット</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2372,11 +2372,11 @@
         <v>2202</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2388,34 +2388,34 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B36">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ホーネット</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2426,20 +2426,20 @@
         <v>2203</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2480,11 +2480,11 @@
         <v>2203</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>スネーク</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2507,11 +2507,11 @@
         <v>2203</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2523,34 +2523,34 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B41">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>スネーク</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2561,20 +2561,20 @@
         <v>2204</v>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2615,11 +2615,11 @@
         <v>2204</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>インプ</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2642,11 +2642,11 @@
         <v>2204</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2658,34 +2658,34 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B46">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>インプ</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2696,20 +2696,20 @@
         <v>2205</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スケルトン</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -2750,11 +2750,11 @@
         <v>2205</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>バット</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2777,11 +2777,11 @@
         <v>2205</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>スケルトン</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2793,34 +2793,34 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B51">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>バット</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2831,20 +2831,20 @@
         <v>3041</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>オーク</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -2858,11 +2858,11 @@
         <v>3041</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>オーク</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2885,11 +2885,11 @@
         <v>3041</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>インプ</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2906,23 +2906,23 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B55">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2939,17 +2939,17 @@
         <v>3042</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>バット</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2966,11 +2966,11 @@
         <v>3042</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>スケルトン</v>
       </c>
       <c r="E57">
         <v>5</v>
@@ -2993,11 +2993,11 @@
         <v>3042</v>
       </c>
       <c r="C58">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スネーク</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -3014,26 +3014,26 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B59">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="C59">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>スケルトン</v>
       </c>
       <c r="E59">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3047,20 +3047,20 @@
         <v>3101</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>シルフ</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3074,11 +3074,11 @@
         <v>3101</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>スライム</v>
       </c>
       <c r="E61">
         <v>5</v>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3095,23 +3095,23 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="B62">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="C62">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E62">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3128,20 +3128,20 @@
         <v>3102</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>シルフ</v>
       </c>
       <c r="E63">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3155,11 +3155,11 @@
         <v>3102</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>スライム</v>
       </c>
       <c r="E64">
         <v>15</v>
@@ -3168,40 +3168,40 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="12" customHeight="1" spans="1:8">
+    <row r="65" spans="1:8">
       <c r="A65">
-        <v>4041</v>
-      </c>
-      <c r="B65" s="2">
-        <v>4041</v>
+        <v>3102</v>
+      </c>
+      <c r="B65">
+        <v>3102</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ビッグラット</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" ht="12" customHeight="1" spans="1:8">
       <c r="A66">
         <v>4041</v>
       </c>
@@ -3209,17 +3209,17 @@
         <v>4041</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3263,11 +3263,11 @@
         <v>4041</v>
       </c>
       <c r="C68">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スライム</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3310,27 +3310,27 @@
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="2">
-        <v>4042</v>
+      <c r="A70">
+        <v>4041</v>
       </c>
       <c r="B70" s="2">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ゴースト</v>
       </c>
       <c r="E70">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -3344,20 +3344,20 @@
         <v>4042</v>
       </c>
       <c r="C71">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>ホーネット</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -3371,11 +3371,11 @@
         <v>4042</v>
       </c>
       <c r="C72">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E72">
         <v>5</v>
@@ -3425,11 +3425,11 @@
         <v>4042</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>インプ</v>
       </c>
       <c r="E74">
         <v>5</v>
@@ -3438,31 +3438,31 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75">
-        <v>4101</v>
-      </c>
-      <c r="B75">
-        <v>4101</v>
+      <c r="A75" s="2">
+        <v>4042</v>
+      </c>
+      <c r="B75" s="2">
+        <v>4042</v>
       </c>
       <c r="C75">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>ホーネット</v>
       </c>
       <c r="E75">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3473,10 +3473,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B76">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="C76">
         <v>104</v>
@@ -3486,7 +3486,7 @@
         <v>イヴィルキング</v>
       </c>
       <c r="E76">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -3500,20 +3500,20 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B77">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>イヴィルキング</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -3540,13 +3540,13 @@
         <v>スケルトン</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3587,11 +3587,11 @@
         <v>5041</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スケルトン</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3634,24 +3634,24 @@
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B82" s="2">
-        <v>5042</v>
+      <c r="A82">
+        <v>5041</v>
+      </c>
+      <c r="B82">
+        <v>5041</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スライム</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -3668,20 +3668,20 @@
         <v>5042</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>スパイダー</v>
       </c>
       <c r="E83">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -3695,11 +3695,11 @@
         <v>5042</v>
       </c>
       <c r="C84">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ウィスプ</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -3722,11 +3722,11 @@
         <v>5042</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>インプ</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -3769,27 +3769,27 @@
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87">
-        <v>5101</v>
-      </c>
-      <c r="B87">
-        <v>5101</v>
+      <c r="A87" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B87" s="2">
+        <v>5042</v>
       </c>
       <c r="C87">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>スパイダー</v>
       </c>
       <c r="E87">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3803,20 +3803,20 @@
         <v>5101</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -3830,11 +3830,11 @@
         <v>5101</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E89">
         <v>10</v>
@@ -3857,11 +3857,11 @@
         <v>5101</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>スライム</v>
       </c>
       <c r="E90">
         <v>10</v>
@@ -3884,11 +3884,11 @@
         <v>5101</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E91">
         <v>10</v>
@@ -3905,26 +3905,26 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B92">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C92">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>ゴースト</v>
       </c>
       <c r="E92">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3938,20 +3938,20 @@
         <v>5102</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ケルベロス</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3965,11 +3965,11 @@
         <v>5102</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E94">
         <v>20</v>
@@ -3992,11 +3992,11 @@
         <v>5102</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>スライム</v>
       </c>
       <c r="E95">
         <v>20</v>
@@ -4019,11 +4019,11 @@
         <v>5102</v>
       </c>
       <c r="C96">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E96">
         <v>20</v>
@@ -4040,26 +4040,26 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B97">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C97">
-        <v>1002</v>
+        <v>11</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>ゴースト</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -4073,20 +4073,20 @@
         <v>6021</v>
       </c>
       <c r="C98">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>エリザベート</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4100,11 +4100,11 @@
         <v>6021</v>
       </c>
       <c r="C99">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>アリエス</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4127,11 +4127,11 @@
         <v>6021</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>1004</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>シイナ</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4154,11 +4154,11 @@
         <v>6021</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4175,23 +4175,23 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B102">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C102">
-        <v>1011</v>
+        <v>1</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>スライム</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4208,17 +4208,17 @@
         <v>6022</v>
       </c>
       <c r="C103">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>セリナ</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -4235,11 +4235,11 @@
         <v>6022</v>
       </c>
       <c r="C104">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>レダ</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4248,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -4262,11 +4262,11 @@
         <v>6022</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>マッドプラント</v>
+        <v>メリアドール</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4289,11 +4289,11 @@
         <v>6022</v>
       </c>
       <c r="C106">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>マッドプラント</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4310,23 +4310,23 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B107">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C107">
-        <v>1001</v>
+        <v>14</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>インプ</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -4343,17 +4343,17 @@
         <v>6031</v>
       </c>
       <c r="C108">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ミカ</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -4370,11 +4370,11 @@
         <v>6031</v>
       </c>
       <c r="C109">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>リシェリ</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4397,11 +4397,11 @@
         <v>6031</v>
       </c>
       <c r="C110">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4424,11 +4424,11 @@
         <v>6031</v>
       </c>
       <c r="C111">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>ユニ</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4445,26 +4445,26 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B112">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C112">
-        <v>201</v>
+        <v>1009</v>
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E112">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4478,20 +4478,20 @@
         <v>6101</v>
       </c>
       <c r="C113">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="D113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -4505,11 +4505,11 @@
         <v>6101</v>
       </c>
       <c r="C114">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C114,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>ゲイザー</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4532,11 +4532,11 @@
         <v>6101</v>
       </c>
       <c r="C115">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C115,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>ゴースト</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -4559,22 +4559,49 @@
         <v>6101</v>
       </c>
       <c r="C116">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
+        <v>ビッグラット</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>6101</v>
+      </c>
+      <c r="B117">
+        <v>6101</v>
+      </c>
+      <c r="C117">
+        <v>13</v>
+      </c>
+      <c r="D117" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
         <v>オーク</v>
       </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-      <c r="F116">
-        <v>0</v>
-      </c>
-      <c r="G116">
-        <v>1</v>
-      </c>
-      <c r="H116">
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
         <v>0</v>
       </c>
     </row>
